--- a/data/trans_dic/IP1003-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen Alergias crónicas</t>
+          <t>Menores que padecen Alergias crónicas (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 12,32</t>
+          <t>3,56; 12,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,68</t>
+          <t>1,61; 9,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,93</t>
+          <t>0,0; 4,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,75</t>
+          <t>1,13; 11,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 10,27</t>
+          <t>1,88; 10,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 13,23</t>
+          <t>3,68; 13,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 17,2</t>
+          <t>4,11; 15,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 22,21</t>
+          <t>5,32; 21,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,56</t>
+          <t>3,47; 9,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,2</t>
+          <t>3,72; 10,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,12</t>
+          <t>2,66; 9,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 14,45</t>
+          <t>4,01; 14,51</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,59</t>
+          <t>3,97; 7,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,89</t>
+          <t>3,15; 6,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,9</t>
+          <t>3,53; 6,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,06</t>
+          <t>4,07; 8,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,72</t>
+          <t>5,73; 9,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,27</t>
+          <t>4,33; 8,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,48</t>
+          <t>3,88; 7,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,32</t>
+          <t>5,83; 10,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 8,15</t>
+          <t>5,29; 7,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,78</t>
+          <t>4,3; 6,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,49</t>
+          <t>4,11; 6,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,64</t>
+          <t>5,5; 8,48</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 9,68</t>
+          <t>3,48; 9,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,96</t>
+          <t>2,16; 7,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,26</t>
+          <t>2,53; 8,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,87</t>
+          <t>2,85; 9,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 10,72</t>
+          <t>3,93; 10,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 9,27</t>
+          <t>3,02; 8,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,05</t>
+          <t>1,37; 5,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,02</t>
+          <t>4,79; 13,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,43; 8,86</t>
+          <t>4,46; 8,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,21</t>
+          <t>2,94; 6,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,95</t>
+          <t>2,36; 5,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 10,18</t>
+          <t>4,54; 9,68</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,46</t>
+          <t>4,71; 7,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,18</t>
+          <t>3,43; 6,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,08</t>
+          <t>3,39; 6,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,09</t>
+          <t>3,97; 7,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 8,47</t>
+          <t>5,67; 8,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,96</t>
+          <t>4,81; 7,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,7</t>
+          <t>3,92; 6,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,45</t>
+          <t>6,47; 10,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,6</t>
+          <t>5,43; 7,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,51</t>
+          <t>4,52; 6,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,92</t>
+          <t>4,04; 5,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,42</t>
+          <t>5,82; 8,32</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen Alergias crónicas (tasa de respuesta: 99,75%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6383</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4393</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4367</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6315</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5752</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7022</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>10750</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10708</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>9186</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3231; 11425</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1481; 8918</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2742</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>617; 6138</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1636; 8940</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3075; 11496</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2821; 10771</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3301; 13508</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6163; 16503</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6519; 17576</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3408; 12055</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4676; 16931</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>23503</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21591</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23343</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26803</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>35222</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30193</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27067</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>40450</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>58726</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>51784</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>50410</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>67252</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>16501; 31725</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14162; 30087</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16695; 31440</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18664; 36721</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>27311; 45169</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21335; 39595</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>18986; 36466</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>30038; 54444</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>47246; 71150</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>40439; 63987</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>39498; 63589</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>53560; 82590</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10753</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7205</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8126</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7637</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10377</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9160</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5781</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>15163</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>21130</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>16365</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13907</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>22800</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>6062; 16200</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3568; 12449</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4372; 14729</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4243; 13811</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6218; 16468</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5189; 15134</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2573; 10697</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8781; 23938</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>14806; 29165</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9903; 23526</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8514; 21572</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>15087; 32147</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>40639</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>33189</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32132</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>36603</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>62635</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>90606</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>78857</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99238</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>32109; 51320</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24255; 43089</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>23846; 43540</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26276; 47673</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>40965; 61839</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>35934; 57765</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>29223; 50166</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>49192; 80052</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>76146; 103890</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>65690; 95026</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>58482; 86083</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>82792; 118415</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1003-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 12,57</t>
+          <t>3,62; 12,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,71</t>
+          <t>1,63; 9,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,62</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 11,23</t>
+          <t>1,14; 12,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 10,29</t>
+          <t>2,28; 10,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 13,76</t>
+          <t>3,41; 13,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 15,7</t>
+          <t>3,92; 15,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 21,79</t>
+          <t>5,15; 22,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,29</t>
+          <t>3,6; 9,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 10,02</t>
+          <t>3,68; 9,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,42</t>
+          <t>2,22; 8,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 14,51</t>
+          <t>3,72; 15,38</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,62</t>
+          <t>4,06; 7,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,7</t>
+          <t>3,21; 6,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,66</t>
+          <t>3,51; 6,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,0</t>
+          <t>3,99; 7,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,47</t>
+          <t>5,68; 9,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,04</t>
+          <t>4,65; 8,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,46</t>
+          <t>3,81; 7,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,58</t>
+          <t>5,71; 10,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 7,97</t>
+          <t>5,29; 7,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,8</t>
+          <t>4,43; 6,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,62</t>
+          <t>4,03; 6,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,48</t>
+          <t>5,52; 8,86</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 9,31</t>
+          <t>3,51; 9,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,53</t>
+          <t>2,32; 7,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 8,53</t>
+          <t>2,41; 8,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 9,29</t>
+          <t>2,54; 8,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,41</t>
+          <t>4,12; 10,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,82</t>
+          <t>2,88; 8,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,71</t>
+          <t>1,22; 5,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 13,06</t>
+          <t>5,0; 13,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,78</t>
+          <t>4,42; 9,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,98</t>
+          <t>3,21; 6,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,99</t>
+          <t>2,34; 5,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,68</t>
+          <t>4,64; 9,89</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,54</t>
+          <t>4,53; 7,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,1</t>
+          <t>3,53; 6,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,18</t>
+          <t>3,35; 5,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,2</t>
+          <t>4,14; 7,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 8,57</t>
+          <t>5,39; 8,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,73</t>
+          <t>4,71; 7,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,74</t>
+          <t>3,98; 6,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,53</t>
+          <t>6,48; 10,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,4</t>
+          <t>5,45; 7,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,54</t>
+          <t>4,49; 6,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,94</t>
+          <t>3,97; 5,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,32</t>
+          <t>5,67; 8,32</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3231; 11425</t>
+          <t>3291; 11199</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1481; 8918</t>
+          <t>1496; 8879</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2742</t>
+          <t>0; 2740</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>617; 6138</t>
+          <t>625; 6630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1636; 8940</t>
+          <t>1981; 9050</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3075; 11496</t>
+          <t>2851; 11243</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2821; 10771</t>
+          <t>2692; 10444</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3301; 13508</t>
+          <t>3194; 13822</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6163; 16503</t>
+          <t>6389; 17552</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6519; 17576</t>
+          <t>6452; 16909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3408; 12055</t>
+          <t>2842; 10848</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4676; 16931</t>
+          <t>4346; 17940</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16501; 31725</t>
+          <t>16890; 32266</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14162; 30087</t>
+          <t>14414; 29938</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16695; 31440</t>
+          <t>16590; 31488</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18664; 36721</t>
+          <t>18336; 36465</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27311; 45169</t>
+          <t>27083; 45780</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21335; 39595</t>
+          <t>22901; 40065</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18986; 36466</t>
+          <t>18618; 36711</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30038; 54444</t>
+          <t>29414; 53353</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47246; 71150</t>
+          <t>47244; 70100</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40439; 63987</t>
+          <t>41754; 64785</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39498; 63589</t>
+          <t>38703; 62063</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53560; 82590</t>
+          <t>53745; 86320</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6062; 16200</t>
+          <t>6118; 16708</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3568; 12449</t>
+          <t>3832; 12578</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4372; 14729</t>
+          <t>4156; 14615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4243; 13811</t>
+          <t>3775; 12765</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6218; 16468</t>
+          <t>6522; 17066</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5189; 15134</t>
+          <t>4940; 14999</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2573; 10697</t>
+          <t>2296; 10890</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8781; 23938</t>
+          <t>9175; 24403</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14806; 29165</t>
+          <t>14691; 30071</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9903; 23526</t>
+          <t>10813; 23173</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8514; 21572</t>
+          <t>8430; 21275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15087; 32147</t>
+          <t>15420; 32828</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32109; 51320</t>
+          <t>30846; 51436</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24255; 43089</t>
+          <t>24901; 44335</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23846; 43540</t>
+          <t>23611; 41695</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26276; 47673</t>
+          <t>27402; 50210</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40965; 61839</t>
+          <t>38946; 62203</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35934; 57765</t>
+          <t>35238; 57423</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29223; 50166</t>
+          <t>29652; 50237</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49192; 80052</t>
+          <t>49293; 79927</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76146; 103890</t>
+          <t>76456; 107054</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65690; 95026</t>
+          <t>65284; 93745</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>58482; 86083</t>
+          <t>57546; 85532</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82792; 118415</t>
+          <t>80718; 118415</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1003-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,02%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 12,32</t>
+          <t>2,33; 10,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 9,66</t>
+          <t>3,67; 13,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>4,1; 17,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 12,13</t>
+          <t>4,92; 22,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 10,42</t>
+          <t>3,49; 12,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 13,46</t>
+          <t>2,18; 9,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 15,22</t>
+          <t>0,0; 5,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 22,29</t>
+          <t>1,39; 13,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,88</t>
+          <t>3,55; 9,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,64</t>
+          <t>3,79; 10,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,48</t>
+          <t>2,4; 9,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 15,38</t>
+          <t>4,18; 15,07</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,87%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,81%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,75</t>
+          <t>5,66; 9,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,67</t>
+          <t>4,56; 8,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,67</t>
+          <t>3,7; 7,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,94</t>
+          <t>5,76; 10,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,6</t>
+          <t>4,07; 7,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,14</t>
+          <t>3,35; 6,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,51</t>
+          <t>3,46; 6,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 10,36</t>
+          <t>4,74; 8,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 7,85</t>
+          <t>5,38; 8,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,88</t>
+          <t>4,47; 6,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,46</t>
+          <t>4,17; 6,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,86</t>
+          <t>5,88; 9,0</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,18%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,36%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,71%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,6</t>
+          <t>3,67; 10,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,61</t>
+          <t>3,1; 9,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 8,46</t>
+          <t>1,5; 6,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 8,58</t>
+          <t>5,42; 13,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 10,79</t>
+          <t>3,71; 9,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,74</t>
+          <t>2,2; 7,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,81</t>
+          <t>2,47; 8,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 13,31</t>
+          <t>2,81; 9,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,05</t>
+          <t>4,43; 8,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,88</t>
+          <t>3,17; 7,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,91</t>
+          <t>2,43; 5,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,89</t>
+          <t>4,84; 10,59</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,97%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,7%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4,56%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,55</t>
+          <t>5,44; 8,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,28</t>
+          <t>4,83; 7,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,92</t>
+          <t>3,92; 6,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,58</t>
+          <t>6,49; 10,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,62</t>
+          <t>4,59; 7,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,68</t>
+          <t>3,45; 6,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,74</t>
+          <t>3,29; 6,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,51</t>
+          <t>4,58; 7,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,63</t>
+          <t>5,46; 7,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 6,45</t>
+          <t>4,51; 6,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 5,9</t>
+          <t>4,01; 5,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 8,32</t>
+          <t>6,13; 8,76</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4367</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6315</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5752</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>6383</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4393</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>664</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2163</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4367</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6315</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5752</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>8754</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3291; 11199</t>
+          <t>2020; 8922</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1496; 8879</t>
+          <t>3067; 11051</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2740</t>
+          <t>2814; 11804</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>625; 6630</t>
+          <t>2789; 12657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1981; 9050</t>
+          <t>3171; 11195</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2851; 11243</t>
+          <t>1999; 8894</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2692; 10444</t>
+          <t>0; 3519</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3194; 13822</t>
+          <t>650; 6376</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6389; 17552</t>
+          <t>6303; 16996</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6452; 16909</t>
+          <t>6642; 17886</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2842; 10848</t>
+          <t>3072; 11674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4346; 17940</t>
+          <t>4328; 15593</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>35222</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30193</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27067</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37292</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>23503</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>21591</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>23343</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26803</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>35222</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30193</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>27067</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40450</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67252</t>
+          <t>64942</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16890; 32266</t>
+          <t>26993; 46355</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14414; 29938</t>
+          <t>22461; 40699</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16590; 31488</t>
+          <t>18102; 36570</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18336; 36465</t>
+          <t>27304; 48383</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27083; 45780</t>
+          <t>16935; 31593</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22901; 40065</t>
+          <t>15044; 30940</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18618; 36711</t>
+          <t>16354; 32603</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29414; 53353</t>
+          <t>20410; 38022</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47244; 70100</t>
+          <t>48092; 72783</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41754; 64785</t>
+          <t>42075; 63829</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38703; 62063</t>
+          <t>40027; 62323</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53745; 86320</t>
+          <t>53195; 81426</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10377</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9160</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5781</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14708</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>10753</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7205</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>8126</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7637</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10377</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9160</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5781</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22800</t>
+          <t>22902</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6118; 16708</t>
+          <t>5810; 16948</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3832; 12578</t>
+          <t>5324; 15907</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4156; 14615</t>
+          <t>2818; 11335</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3775; 12765</t>
+          <t>9132; 22774</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6522; 17066</t>
+          <t>6451; 16853</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4940; 14999</t>
+          <t>3636; 13157</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2296; 10890</t>
+          <t>4263; 14262</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9175; 24403</t>
+          <t>4195; 14171</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14691; 30071</t>
+          <t>14712; 29431</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10813; 23173</t>
+          <t>10663; 24287</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8430; 21275</t>
+          <t>8738; 21437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15420; 32828</t>
+          <t>15381; 33631</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>58479</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>40639</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>33189</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>32132</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>36603</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>49967</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>45668</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38600</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62635</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>96599</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30846; 51436</t>
+          <t>39270; 61155</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24901; 44335</t>
+          <t>36105; 59535</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23611; 41695</t>
+          <t>29165; 49869</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27402; 50210</t>
+          <t>45376; 72397</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38946; 62203</t>
+          <t>31291; 50830</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35238; 57423</t>
+          <t>24394; 43668</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29652; 50237</t>
+          <t>23158; 42850</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49293; 79927</t>
+          <t>28734; 49207</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76456; 107054</t>
+          <t>76570; 106562</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65284; 93745</t>
+          <t>65502; 94597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57546; 85532</t>
+          <t>58078; 85840</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80718; 118415</t>
+          <t>81305; 116227</t>
         </is>
       </c>
     </row>
